--- a/test/jd_smoke.xlsx
+++ b/test/jd_smoke.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,6 +583,21 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>最近用京东鸿蒙版买东西，体验真的越来越差了，尤其是打开商品详情页的时候，往下滑动查看图文详情那叫一个卡，画面一顿一顿的，根本不跟手，手指都划过去了画面还停在原地，得等个一两秒才蹭过去，特别影响购物心情。而且不光是详情页，搜索结果页的商品列表往下滑也卡，瀑布流加载新的商品卡片时整个屏幕像掉帧一样，滑动过程中还会误触点进某个商品详情，特别烦人。我以为是手机问题，重启了手机、清了京东缓存、甚至把京东卸载重装了一遍，结果还是一模一样地卡。我的手机是华为Mate60，鸿蒙系统也是最新版本，其他App比如淘宝拼多多滑动都很流畅，就京东这样。已经连续好几个版本都这样了，从15.2.10更新到现在这个版本一点改善都没有，反而感觉更卡了。再加上商品详情页里的主图视频点开播放也是一卡一卡的，首帧黑屏要等好几秒才开始动，播放过程中画面还会突然卡住但声音继续，音画不同步很严重，看个商品介绍视频都费劲。还有购物车页面，点结算按钮经常半天才跳转，有时候点了好几次都没反应，以为自己没点上又多点几下结果跳了好几个页面。希望京东赶紧全面优化一下滑动和加载性能，不然真的要考虑换别的平台买东西了，毕竟买东西本来就图个方便顺畅，现在用着这么卡真的很影响体验，强烈要求尽快修复这些卡顿和响应慢的问题。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15.2.20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
